--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Programming\Python Projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Programming\Portfolio\guide-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F788AAF9-E0C1-4C8C-AF72-D47C37B8B797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362C6E22-005C-4C40-A31D-8F3292F9F473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22428" yWindow="420" windowWidth="21600" windowHeight="11832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updates" sheetId="5" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="635">
   <si>
     <t>Main Folder</t>
   </si>
@@ -2834,7 +2834,10 @@
     <t>GEN026</t>
   </si>
   <si>
-    <t>Todays update !!</t>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>New Update</t>
   </si>
 </sst>
 </file>
@@ -3574,100 +3577,100 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3951,16 +3954,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825AAD22-E8D8-45EA-B8B8-D05372AA537B}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" style="54" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="55" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" style="112" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" style="54" customWidth="1"/>
+    <col min="2" max="2" width="13" style="55" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" style="112" customWidth="1"/>
     <col min="4" max="4" width="15" style="112" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.88671875" style="112" customWidth="1"/>
+    <col min="5" max="5" width="54.85546875" style="112" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="53" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="53" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="105" t="s">
         <v>327</v>
       </c>
@@ -3977,7 +3980,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="78" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A2" s="107" t="s">
         <v>276</v>
       </c>
@@ -3994,7 +3997,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A3" s="107" t="s">
         <v>279</v>
       </c>
@@ -4011,7 +4014,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A4" s="107" t="s">
         <v>282</v>
       </c>
@@ -4028,7 +4031,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="78" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A5" s="109" t="s">
         <v>284</v>
       </c>
@@ -4045,7 +4048,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="78" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A6" s="109" t="s">
         <v>287</v>
       </c>
@@ -4062,7 +4065,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="126" x14ac:dyDescent="0.25">
       <c r="A7" s="109" t="s">
         <v>288</v>
       </c>
@@ -4079,7 +4082,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="78" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A8" s="107" t="s">
         <v>290</v>
       </c>
@@ -4096,7 +4099,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="78" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A9" s="107" t="s">
         <v>292</v>
       </c>
@@ -4113,7 +4116,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="234" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="236.25" x14ac:dyDescent="0.25">
       <c r="A10" s="107" t="s">
         <v>294</v>
       </c>
@@ -4130,7 +4133,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A11" s="109" t="s">
         <v>296</v>
       </c>
@@ -4147,7 +4150,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A12" s="109" t="s">
         <v>298</v>
       </c>
@@ -4164,7 +4167,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="78" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A13" s="109" t="s">
         <v>300</v>
       </c>
@@ -4181,7 +4184,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="107" t="s">
         <v>302</v>
       </c>
@@ -4198,7 +4201,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A15" s="107" t="s">
         <v>304</v>
       </c>
@@ -4215,7 +4218,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A16" s="107" t="s">
         <v>306</v>
       </c>
@@ -4232,7 +4235,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A17" s="109" t="s">
         <v>307</v>
       </c>
@@ -4249,7 +4252,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="109" t="s">
         <v>309</v>
       </c>
@@ -4266,7 +4269,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="63" x14ac:dyDescent="0.25">
       <c r="A19" s="109" t="s">
         <v>311</v>
       </c>
@@ -4283,7 +4286,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="78" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A20" s="109" t="s">
         <v>314</v>
       </c>
@@ -4300,7 +4303,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A21" s="109" t="s">
         <v>316</v>
       </c>
@@ -4317,7 +4320,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A22" s="109" t="s">
         <v>318</v>
       </c>
@@ -4334,7 +4337,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A23" s="109" t="s">
         <v>320</v>
       </c>
@@ -4351,7 +4354,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A24" s="109" t="s">
         <v>321</v>
       </c>
@@ -4368,7 +4371,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25" s="109" t="s">
         <v>322</v>
       </c>
@@ -4385,7 +4388,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="109" t="s">
         <v>328</v>
       </c>
@@ -4402,24 +4405,24 @@
         <v>329</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="109" t="s">
         <v>632</v>
       </c>
       <c r="B27" s="111">
-        <v>45525</v>
+        <v>45580</v>
       </c>
       <c r="C27" s="109" t="s">
-        <v>323</v>
+        <v>633</v>
       </c>
       <c r="D27" s="109" t="s">
-        <v>297</v>
+        <v>633</v>
       </c>
       <c r="E27" s="110" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="109"/>
       <c r="B28" s="111"/>
       <c r="C28" s="109"/>
@@ -4434,16 +4437,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DC9654D-8F81-476F-BBA5-729F201942DB}">
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="60.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -4460,7 +4463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>5</v>
       </c>
@@ -4475,7 +4478,7 @@
       </c>
       <c r="E2" s="28"/>
     </row>
-    <row r="3" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>5</v>
       </c>
@@ -4490,7 +4493,7 @@
       </c>
       <c r="E3" s="25"/>
     </row>
-    <row r="4" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>5</v>
       </c>
@@ -4505,7 +4508,7 @@
       </c>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
         <v>5</v>
       </c>
@@ -4522,7 +4525,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
         <v>5</v>
       </c>
@@ -4537,7 +4540,7 @@
       </c>
       <c r="E6" s="30"/>
     </row>
-    <row r="7" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
         <v>5</v>
       </c>
@@ -4552,7 +4555,7 @@
       </c>
       <c r="E7" s="31"/>
     </row>
-    <row r="8" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
         <v>5</v>
       </c>
@@ -4567,7 +4570,7 @@
       </c>
       <c r="E8" s="23"/>
     </row>
-    <row r="9" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
         <v>5</v>
       </c>
@@ -4582,7 +4585,7 @@
       </c>
       <c r="E9" s="25"/>
     </row>
-    <row r="10" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="26" t="s">
         <v>5</v>
       </c>
@@ -4597,7 +4600,7 @@
       </c>
       <c r="E10" s="23"/>
     </row>
-    <row r="11" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="26" t="s">
         <v>5</v>
       </c>
@@ -4612,7 +4615,7 @@
       </c>
       <c r="E11" s="24"/>
     </row>
-    <row r="12" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="26" t="s">
         <v>5</v>
       </c>
@@ -4627,7 +4630,7 @@
       </c>
       <c r="E12" s="24"/>
     </row>
-    <row r="13" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="26" t="s">
         <v>5</v>
       </c>
@@ -4642,7 +4645,7 @@
       </c>
       <c r="E13" s="25"/>
     </row>
-    <row r="14" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
         <v>5</v>
       </c>
@@ -4657,7 +4660,7 @@
       </c>
       <c r="E14" s="23"/>
     </row>
-    <row r="15" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="26" t="s">
         <v>5</v>
       </c>
@@ -4672,7 +4675,7 @@
       </c>
       <c r="E15" s="24"/>
     </row>
-    <row r="16" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="26" t="s">
         <v>5</v>
       </c>
@@ -4687,7 +4690,7 @@
       </c>
       <c r="E16" s="25"/>
     </row>
-    <row r="17" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="26" t="s">
         <v>5</v>
       </c>
@@ -4702,7 +4705,7 @@
       </c>
       <c r="E17" s="23"/>
     </row>
-    <row r="18" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="s">
         <v>5</v>
       </c>
@@ -4717,7 +4720,7 @@
       </c>
       <c r="E18" s="24"/>
     </row>
-    <row r="19" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="26" t="s">
         <v>5</v>
       </c>
@@ -4732,7 +4735,7 @@
       </c>
       <c r="E19" s="24"/>
     </row>
-    <row r="20" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="26" t="s">
         <v>5</v>
       </c>
@@ -4747,7 +4750,7 @@
       </c>
       <c r="E20" s="25"/>
     </row>
-    <row r="21" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="26" t="s">
         <v>5</v>
       </c>
@@ -4764,7 +4767,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="26" t="s">
         <v>5</v>
       </c>
@@ -4779,7 +4782,7 @@
       </c>
       <c r="E22" s="23"/>
     </row>
-    <row r="23" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="26" t="s">
         <v>5</v>
       </c>
@@ -4794,7 +4797,7 @@
       </c>
       <c r="E23" s="24"/>
     </row>
-    <row r="24" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="26" t="s">
         <v>5</v>
       </c>
@@ -4809,7 +4812,7 @@
       </c>
       <c r="E24" s="24"/>
     </row>
-    <row r="25" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="26" t="s">
         <v>5</v>
       </c>
@@ -4824,7 +4827,7 @@
       </c>
       <c r="E25" s="24"/>
     </row>
-    <row r="26" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="26" t="s">
         <v>5</v>
       </c>
@@ -4839,7 +4842,7 @@
       </c>
       <c r="E26" s="24"/>
     </row>
-    <row r="27" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="26" t="s">
         <v>5</v>
       </c>
@@ -4854,7 +4857,7 @@
       </c>
       <c r="E27" s="25"/>
     </row>
-    <row r="28" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="26" t="s">
         <v>5</v>
       </c>
@@ -4869,7 +4872,7 @@
       </c>
       <c r="E28" s="23"/>
     </row>
-    <row r="29" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="26" t="s">
         <v>5</v>
       </c>
@@ -4884,7 +4887,7 @@
       </c>
       <c r="E29" s="24"/>
     </row>
-    <row r="30" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="26" t="s">
         <v>5</v>
       </c>
@@ -4899,7 +4902,7 @@
       </c>
       <c r="E30" s="24"/>
     </row>
-    <row r="31" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="26" t="s">
         <v>5</v>
       </c>
@@ -4914,7 +4917,7 @@
       </c>
       <c r="E31" s="24"/>
     </row>
-    <row r="32" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="26" t="s">
         <v>5</v>
       </c>
@@ -4929,7 +4932,7 @@
       </c>
       <c r="E32" s="25"/>
     </row>
-    <row r="33" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="26" t="s">
         <v>5</v>
       </c>
@@ -4944,7 +4947,7 @@
       </c>
       <c r="E33" s="23"/>
     </row>
-    <row r="34" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="26" t="s">
         <v>5</v>
       </c>
@@ -4959,7 +4962,7 @@
       </c>
       <c r="E34" s="24"/>
     </row>
-    <row r="35" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="26" t="s">
         <v>5</v>
       </c>
@@ -4974,7 +4977,7 @@
       </c>
       <c r="E35" s="25"/>
     </row>
-    <row r="36" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="26" t="s">
         <v>5</v>
       </c>
@@ -4989,7 +4992,7 @@
       </c>
       <c r="E36" s="23"/>
     </row>
-    <row r="37" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="26" t="s">
         <v>5</v>
       </c>
@@ -5004,7 +5007,7 @@
       </c>
       <c r="E37" s="24"/>
     </row>
-    <row r="38" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="26" t="s">
         <v>5</v>
       </c>
@@ -5019,7 +5022,7 @@
       </c>
       <c r="E38" s="24"/>
     </row>
-    <row r="39" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="26" t="s">
         <v>5</v>
       </c>
@@ -5034,7 +5037,7 @@
       </c>
       <c r="E39" s="24"/>
     </row>
-    <row r="40" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="26" t="s">
         <v>5</v>
       </c>
@@ -5049,7 +5052,7 @@
       </c>
       <c r="E40" s="24"/>
     </row>
-    <row r="41" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>5</v>
       </c>
@@ -5064,7 +5067,7 @@
       </c>
       <c r="E41" s="24"/>
     </row>
-    <row r="42" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="26" t="s">
         <v>5</v>
       </c>
@@ -5079,7 +5082,7 @@
       </c>
       <c r="E42" s="24"/>
     </row>
-    <row r="43" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>5</v>
       </c>
@@ -5094,7 +5097,7 @@
       </c>
       <c r="E43" s="25"/>
     </row>
-    <row r="44" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="26" t="s">
         <v>5</v>
       </c>
@@ -5109,7 +5112,7 @@
       </c>
       <c r="E44" s="23"/>
     </row>
-    <row r="45" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="26" t="s">
         <v>5</v>
       </c>
@@ -5124,7 +5127,7 @@
       </c>
       <c r="E45" s="24"/>
     </row>
-    <row r="46" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="26" t="s">
         <v>5</v>
       </c>
@@ -5139,7 +5142,7 @@
       </c>
       <c r="E46" s="24"/>
     </row>
-    <row r="47" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="26" t="s">
         <v>5</v>
       </c>
@@ -5154,7 +5157,7 @@
       </c>
       <c r="E47" s="24"/>
     </row>
-    <row r="48" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="26" t="s">
         <v>5</v>
       </c>
@@ -5169,7 +5172,7 @@
       </c>
       <c r="E48" s="24"/>
     </row>
-    <row r="49" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="26" t="s">
         <v>5</v>
       </c>
@@ -5184,7 +5187,7 @@
       </c>
       <c r="E49" s="24"/>
     </row>
-    <row r="50" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="26" t="s">
         <v>5</v>
       </c>
@@ -5199,7 +5202,7 @@
       </c>
       <c r="E50" s="24"/>
     </row>
-    <row r="51" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="26" t="s">
         <v>5</v>
       </c>
@@ -5214,7 +5217,7 @@
       </c>
       <c r="E51" s="24"/>
     </row>
-    <row r="52" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="26" t="s">
         <v>5</v>
       </c>
@@ -5229,7 +5232,7 @@
       </c>
       <c r="E52" s="24"/>
     </row>
-    <row r="53" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="26" t="s">
         <v>5</v>
       </c>
@@ -5244,7 +5247,7 @@
       </c>
       <c r="E53" s="25"/>
     </row>
-    <row r="54" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="26" t="s">
         <v>5</v>
       </c>
@@ -5259,7 +5262,7 @@
       </c>
       <c r="E54" s="23"/>
     </row>
-    <row r="55" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="26" t="s">
         <v>5</v>
       </c>
@@ -5274,7 +5277,7 @@
       </c>
       <c r="E55" s="24"/>
     </row>
-    <row r="56" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="26" t="s">
         <v>5</v>
       </c>
@@ -5289,7 +5292,7 @@
       </c>
       <c r="E56" s="25"/>
     </row>
-    <row r="57" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="26" t="s">
         <v>5</v>
       </c>
@@ -5304,7 +5307,7 @@
       </c>
       <c r="E57" s="23"/>
     </row>
-    <row r="58" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="26" t="s">
         <v>5</v>
       </c>
@@ -5319,7 +5322,7 @@
       </c>
       <c r="E58" s="24"/>
     </row>
-    <row r="59" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="26" t="s">
         <v>5</v>
       </c>
@@ -5334,7 +5337,7 @@
       </c>
       <c r="E59" s="24"/>
     </row>
-    <row r="60" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="26" t="s">
         <v>5</v>
       </c>
@@ -5349,7 +5352,7 @@
       </c>
       <c r="E60" s="25"/>
     </row>
-    <row r="61" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="26" t="s">
         <v>5</v>
       </c>
@@ -5364,7 +5367,7 @@
       </c>
       <c r="E61" s="23"/>
     </row>
-    <row r="62" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="26" t="s">
         <v>5</v>
       </c>
@@ -5379,7 +5382,7 @@
       </c>
       <c r="E62" s="24"/>
     </row>
-    <row r="63" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="26" t="s">
         <v>5</v>
       </c>
@@ -5394,7 +5397,7 @@
       </c>
       <c r="E63" s="24"/>
     </row>
-    <row r="64" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="26" t="s">
         <v>5</v>
       </c>
@@ -5409,7 +5412,7 @@
       </c>
       <c r="E64" s="25"/>
     </row>
-    <row r="65" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="26" t="s">
         <v>5</v>
       </c>
@@ -5424,7 +5427,7 @@
       </c>
       <c r="E65" s="23"/>
     </row>
-    <row r="66" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="26" t="s">
         <v>5</v>
       </c>
@@ -5439,7 +5442,7 @@
       </c>
       <c r="E66" s="24"/>
     </row>
-    <row r="67" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="26" t="s">
         <v>5</v>
       </c>
@@ -5454,7 +5457,7 @@
       </c>
       <c r="E67" s="24"/>
     </row>
-    <row r="68" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="26" t="s">
         <v>5</v>
       </c>
@@ -5469,7 +5472,7 @@
       </c>
       <c r="E68" s="24"/>
     </row>
-    <row r="69" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="26" t="s">
         <v>5</v>
       </c>
@@ -5484,7 +5487,7 @@
       </c>
       <c r="E69" s="24"/>
     </row>
-    <row r="70" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="26" t="s">
         <v>5</v>
       </c>
@@ -5499,7 +5502,7 @@
       </c>
       <c r="E70" s="24"/>
     </row>
-    <row r="71" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="26" t="s">
         <v>5</v>
       </c>
@@ -5514,7 +5517,7 @@
       </c>
       <c r="E71" s="24"/>
     </row>
-    <row r="72" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="26" t="s">
         <v>5</v>
       </c>
@@ -5529,7 +5532,7 @@
       </c>
       <c r="E72" s="24"/>
     </row>
-    <row r="73" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="26" t="s">
         <v>5</v>
       </c>
@@ -5544,7 +5547,7 @@
       </c>
       <c r="E73" s="25"/>
     </row>
-    <row r="74" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="26" t="s">
         <v>5</v>
       </c>
@@ -5559,7 +5562,7 @@
       </c>
       <c r="E74" s="23"/>
     </row>
-    <row r="75" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="26" t="s">
         <v>5</v>
       </c>
@@ -5574,7 +5577,7 @@
       </c>
       <c r="E75" s="24"/>
     </row>
-    <row r="76" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="26" t="s">
         <v>5</v>
       </c>
@@ -5589,7 +5592,7 @@
       </c>
       <c r="E76" s="24"/>
     </row>
-    <row r="77" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="26" t="s">
         <v>5</v>
       </c>
@@ -5604,7 +5607,7 @@
       </c>
       <c r="E77" s="24"/>
     </row>
-    <row r="78" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="26" t="s">
         <v>5</v>
       </c>
@@ -5619,7 +5622,7 @@
       </c>
       <c r="E78" s="24"/>
     </row>
-    <row r="79" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="26" t="s">
         <v>5</v>
       </c>
@@ -5634,7 +5637,7 @@
       </c>
       <c r="E79" s="24"/>
     </row>
-    <row r="80" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="26" t="s">
         <v>5</v>
       </c>
@@ -5649,7 +5652,7 @@
       </c>
       <c r="E80" s="24"/>
     </row>
-    <row r="81" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="26" t="s">
         <v>5</v>
       </c>
@@ -5664,7 +5667,7 @@
       </c>
       <c r="E81" s="24"/>
     </row>
-    <row r="82" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="26" t="s">
         <v>5</v>
       </c>
@@ -5679,7 +5682,7 @@
       </c>
       <c r="E82" s="24"/>
     </row>
-    <row r="83" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="26" t="s">
         <v>5</v>
       </c>
@@ -5694,7 +5697,7 @@
       </c>
       <c r="E83" s="24"/>
     </row>
-    <row r="84" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="26" t="s">
         <v>5</v>
       </c>
@@ -5709,7 +5712,7 @@
       </c>
       <c r="E84" s="25"/>
     </row>
-    <row r="85" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="26" t="s">
         <v>5</v>
       </c>
@@ -5724,7 +5727,7 @@
       </c>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="26" t="s">
         <v>5</v>
       </c>
@@ -5739,7 +5742,7 @@
       </c>
       <c r="E86" s="11"/>
     </row>
-    <row r="87" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="26" t="s">
         <v>5</v>
       </c>
@@ -5754,7 +5757,7 @@
       </c>
       <c r="E87" s="23"/>
     </row>
-    <row r="88" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="26" t="s">
         <v>5</v>
       </c>
@@ -5769,7 +5772,7 @@
       </c>
       <c r="E88" s="24"/>
     </row>
-    <row r="89" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="26" t="s">
         <v>5</v>
       </c>
@@ -5784,7 +5787,7 @@
       </c>
       <c r="E89" s="24"/>
     </row>
-    <row r="90" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="26" t="s">
         <v>5</v>
       </c>
@@ -5799,7 +5802,7 @@
       </c>
       <c r="E90" s="25"/>
     </row>
-    <row r="91" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="26" t="s">
         <v>5</v>
       </c>
@@ -5814,7 +5817,7 @@
       </c>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="26" t="s">
         <v>5</v>
       </c>
@@ -5829,7 +5832,7 @@
       </c>
       <c r="E92" s="6"/>
     </row>
-    <row r="93" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="26" t="s">
         <v>5</v>
       </c>
@@ -5844,7 +5847,7 @@
       </c>
       <c r="E93" s="23"/>
     </row>
-    <row r="94" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="26" t="s">
         <v>5</v>
       </c>
@@ -5859,7 +5862,7 @@
       </c>
       <c r="E94" s="25"/>
     </row>
-    <row r="95" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="26" t="s">
         <v>5</v>
       </c>
@@ -5873,7 +5876,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="26" t="s">
         <v>5</v>
       </c>
@@ -5887,7 +5890,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="26" t="s">
         <v>5</v>
       </c>
@@ -5901,7 +5904,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="26" t="s">
         <v>5</v>
       </c>
@@ -5915,7 +5918,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
         <v>5</v>
       </c>
@@ -5937,16 +5940,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CA25645-6F60-48C1-90EE-23AEE1553F08}">
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5546875" customWidth="1"/>
-    <col min="3" max="3" width="45.21875" customWidth="1"/>
-    <col min="4" max="4" width="82.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.6640625" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+    <col min="3" max="3" width="45.28515625" customWidth="1"/>
+    <col min="4" max="4" width="82.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
@@ -5963,7 +5966,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>5</v>
       </c>
@@ -5978,7 +5981,7 @@
       </c>
       <c r="E2" s="60"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="73" t="s">
         <v>5</v>
       </c>
@@ -5993,7 +5996,7 @@
       </c>
       <c r="E3" s="65"/>
     </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
         <v>5</v>
       </c>
@@ -6008,7 +6011,7 @@
       </c>
       <c r="E4" s="56"/>
     </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="73" t="s">
         <v>5</v>
       </c>
@@ -6023,7 +6026,7 @@
       </c>
       <c r="E5" s="56"/>
     </row>
-    <row r="6" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="73" t="s">
         <v>5</v>
       </c>
@@ -6038,7 +6041,7 @@
       </c>
       <c r="E6" s="56"/>
     </row>
-    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="73" t="s">
         <v>5</v>
       </c>
@@ -6053,7 +6056,7 @@
       </c>
       <c r="E7" s="56"/>
     </row>
-    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="73" t="s">
         <v>5</v>
       </c>
@@ -6068,7 +6071,7 @@
       </c>
       <c r="E8" s="56"/>
     </row>
-    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="73" t="s">
         <v>5</v>
       </c>
@@ -6083,7 +6086,7 @@
       </c>
       <c r="E9" s="56"/>
     </row>
-    <row r="10" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="73" t="s">
         <v>5</v>
       </c>
@@ -6098,7 +6101,7 @@
       </c>
       <c r="E10" s="57"/>
     </row>
-    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="73" t="s">
         <v>5</v>
       </c>
@@ -6113,7 +6116,7 @@
       </c>
       <c r="E11" s="56"/>
     </row>
-    <row r="12" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A12" s="73" t="s">
         <v>5</v>
       </c>
@@ -6128,7 +6131,7 @@
       </c>
       <c r="E12" s="57"/>
     </row>
-    <row r="13" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A13" s="73" t="s">
         <v>5</v>
       </c>
@@ -6143,7 +6146,7 @@
       </c>
       <c r="E13" s="57"/>
     </row>
-    <row r="14" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="73" t="s">
         <v>5</v>
       </c>
@@ -6158,7 +6161,7 @@
       </c>
       <c r="E14" s="56"/>
     </row>
-    <row r="15" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="73" t="s">
         <v>5</v>
       </c>
@@ -6173,7 +6176,7 @@
       </c>
       <c r="E15" s="56"/>
     </row>
-    <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="73" t="s">
         <v>5</v>
       </c>
@@ -6188,7 +6191,7 @@
       </c>
       <c r="E16" s="56"/>
     </row>
-    <row r="17" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="73" t="s">
         <v>5</v>
       </c>
@@ -6203,7 +6206,7 @@
       </c>
       <c r="E17" s="56"/>
     </row>
-    <row r="18" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="73" t="s">
         <v>5</v>
       </c>
@@ -6218,7 +6221,7 @@
       </c>
       <c r="E18" s="57"/>
     </row>
-    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="73" t="s">
         <v>5</v>
       </c>
@@ -6233,7 +6236,7 @@
       </c>
       <c r="E19" s="56"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="73" t="s">
         <v>5</v>
       </c>
@@ -6248,7 +6251,7 @@
       </c>
       <c r="E20" s="56"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="74" t="s">
         <v>5</v>
       </c>
@@ -6263,7 +6266,7 @@
       </c>
       <c r="E21" s="68"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="74" t="s">
         <v>5</v>
       </c>
@@ -6278,7 +6281,7 @@
       </c>
       <c r="E22" s="68"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="74" t="s">
         <v>5</v>
       </c>
@@ -6293,7 +6296,7 @@
       </c>
       <c r="E23" s="68"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="74" t="s">
         <v>5</v>
       </c>
@@ -6308,7 +6311,7 @@
       </c>
       <c r="E24" s="68"/>
     </row>
-    <row r="25" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="73" t="s">
         <v>5</v>
       </c>
@@ -6323,7 +6326,7 @@
       </c>
       <c r="E25" s="56"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="74" t="s">
         <v>5</v>
       </c>
@@ -6338,7 +6341,7 @@
       </c>
       <c r="E26" s="68"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="73" t="s">
         <v>5</v>
       </c>
@@ -6353,7 +6356,7 @@
       </c>
       <c r="E27" s="56"/>
     </row>
-    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="73" t="s">
         <v>5</v>
       </c>
@@ -6368,7 +6371,7 @@
       </c>
       <c r="E28" s="56"/>
     </row>
-    <row r="29" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="73" t="s">
         <v>5</v>
       </c>
@@ -6383,7 +6386,7 @@
       </c>
       <c r="E29" s="56"/>
     </row>
-    <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="73" t="s">
         <v>5</v>
       </c>
@@ -6398,7 +6401,7 @@
       </c>
       <c r="E30" s="56"/>
     </row>
-    <row r="31" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="73" t="s">
         <v>5</v>
       </c>
@@ -6413,7 +6416,7 @@
       </c>
       <c r="E31" s="56"/>
     </row>
-    <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="73" t="s">
         <v>5</v>
       </c>
@@ -6428,7 +6431,7 @@
       </c>
       <c r="E32" s="56"/>
     </row>
-    <row r="33" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A33" s="73" t="s">
         <v>5</v>
       </c>
@@ -6445,7 +6448,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A34" s="73" t="s">
         <v>5</v>
       </c>
@@ -6460,7 +6463,7 @@
       </c>
       <c r="E34" s="56"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="74" t="s">
         <v>5</v>
       </c>
@@ -6475,7 +6478,7 @@
       </c>
       <c r="E35" s="68"/>
     </row>
-    <row r="36" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A36" s="73" t="s">
         <v>5</v>
       </c>
@@ -6490,7 +6493,7 @@
       </c>
       <c r="E36" s="56"/>
     </row>
-    <row r="37" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="73" t="s">
         <v>5</v>
       </c>
@@ -6505,7 +6508,7 @@
       </c>
       <c r="E37" s="56"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="74" t="s">
         <v>5</v>
       </c>
@@ -6520,7 +6523,7 @@
       </c>
       <c r="E38" s="68"/>
     </row>
-    <row r="39" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A39" s="73" t="s">
         <v>5</v>
       </c>
@@ -6537,7 +6540,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="73" t="s">
         <v>5</v>
       </c>
@@ -6552,7 +6555,7 @@
       </c>
       <c r="E40" s="56"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="73" t="s">
         <v>5</v>
       </c>
@@ -6567,7 +6570,7 @@
       </c>
       <c r="E41" s="56"/>
     </row>
-    <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="73" t="s">
         <v>5</v>
       </c>
@@ -6582,7 +6585,7 @@
       </c>
       <c r="E42" s="56"/>
     </row>
-    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="75" t="s">
         <v>5</v>
       </c>
@@ -6605,17 +6608,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F53C648C-CF69-4139-886D-FC43B831BDB6}">
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.88671875" style="52" customWidth="1"/>
-    <col min="2" max="2" width="33.44140625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="40.44140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="54.44140625" style="20" customWidth="1"/>
-    <col min="5" max="5" width="60.109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="26.85546875" style="52" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="40.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.42578125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="60.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="51" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="51" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -6632,130 +6635,130 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="115" t="s">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="142" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="117" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="128" t="s">
+      <c r="B2" s="143" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="144" t="s">
         <v>92</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="113"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="116"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="125"/>
+      <c r="E2" s="141"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="124"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="122"/>
       <c r="D3" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="114"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="119" t="s">
+      <c r="E3" s="128"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="123" t="s">
+      <c r="B4" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="117" t="s">
         <v>95</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="126"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="120"/>
-      <c r="B5" s="122"/>
-      <c r="C5" s="124"/>
+      <c r="E4" s="127"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="123"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="121"/>
       <c r="D5" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="127"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="120"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="124"/>
+      <c r="E5" s="129"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="123"/>
+      <c r="B6" s="125"/>
+      <c r="C6" s="121"/>
       <c r="D6" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="127"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="116"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="125"/>
+      <c r="E6" s="129"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="124"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="122"/>
       <c r="D7" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="114"/>
-    </row>
-    <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="119" t="s">
+      <c r="E7" s="128"/>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="123" t="s">
+      <c r="B8" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="117" t="s">
         <v>100</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="126"/>
-    </row>
-    <row r="9" spans="1:5" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="116"/>
-      <c r="B9" s="118"/>
-      <c r="C9" s="125"/>
+      <c r="E8" s="127"/>
+    </row>
+    <row r="9" spans="1:5" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="124"/>
+      <c r="B9" s="126"/>
+      <c r="C9" s="122"/>
       <c r="D9" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="114"/>
-    </row>
-    <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="119" t="s">
+      <c r="E9" s="128"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="123" t="s">
+      <c r="B10" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="117" t="s">
         <v>103</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="123" t="s">
+      <c r="E10" s="117" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="116"/>
-      <c r="B11" s="118"/>
-      <c r="C11" s="125"/>
+    <row r="11" spans="1:5" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="124"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="122"/>
       <c r="D11" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="125"/>
-    </row>
-    <row r="12" spans="1:5" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="119" t="s">
+      <c r="E11" s="122"/>
+    </row>
+    <row r="12" spans="1:5" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="123" t="s">
+      <c r="B12" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="117" t="s">
         <v>107</v>
       </c>
       <c r="D12" s="14" t="s">
@@ -6765,10 +6768,10 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="120"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="124"/>
+    <row r="13" spans="1:5" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="123"/>
+      <c r="B13" s="125"/>
+      <c r="C13" s="121"/>
       <c r="D13" s="15" t="s">
         <v>109</v>
       </c>
@@ -6776,10 +6779,10 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="120"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="124"/>
+    <row r="14" spans="1:5" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="123"/>
+      <c r="B14" s="125"/>
+      <c r="C14" s="121"/>
       <c r="D14" s="15" t="s">
         <v>110</v>
       </c>
@@ -6787,10 +6790,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="120"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="124"/>
+    <row r="15" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="123"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="121"/>
       <c r="D15" s="15" t="s">
         <v>111</v>
       </c>
@@ -6798,65 +6801,65 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="120"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="124"/>
+    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="123"/>
+      <c r="B16" s="125"/>
+      <c r="C16" s="121"/>
       <c r="D16" s="15" t="s">
         <v>112</v>
       </c>
       <c r="E16" s="33"/>
     </row>
-    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="116"/>
-      <c r="B17" s="118"/>
-      <c r="C17" s="125"/>
+    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="124"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="122"/>
       <c r="D17" s="16" t="s">
         <v>113</v>
       </c>
       <c r="E17" s="34"/>
     </row>
-    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="119" t="s">
+    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B18" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="123" t="s">
+      <c r="B18" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="117" t="s">
         <v>118</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="E18" s="129"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="120"/>
-      <c r="B19" s="122"/>
-      <c r="C19" s="124"/>
+      <c r="E18" s="119"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="123"/>
+      <c r="B19" s="125"/>
+      <c r="C19" s="121"/>
       <c r="D19" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="130"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="116"/>
-      <c r="B20" s="118"/>
-      <c r="C20" s="125"/>
+      <c r="E19" s="131"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="124"/>
+      <c r="B20" s="126"/>
+      <c r="C20" s="122"/>
       <c r="D20" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="131"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="119" t="s">
+      <c r="E20" s="130"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="123" t="s">
+      <c r="B21" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="117" t="s">
         <v>122</v>
       </c>
       <c r="D21" s="14" t="s">
@@ -6866,10 +6869,10 @@
         <v>138</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="120"/>
-      <c r="B22" s="122"/>
-      <c r="C22" s="124"/>
+    <row r="22" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="123"/>
+      <c r="B22" s="125"/>
+      <c r="C22" s="121"/>
       <c r="D22" s="15" t="s">
         <v>124</v>
       </c>
@@ -6877,10 +6880,10 @@
         <v>139</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="120"/>
-      <c r="B23" s="122"/>
-      <c r="C23" s="124"/>
+    <row r="23" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="123"/>
+      <c r="B23" s="125"/>
+      <c r="C23" s="121"/>
       <c r="D23" s="15" t="s">
         <v>125</v>
       </c>
@@ -6888,10 +6891,10 @@
         <v>140</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="120"/>
-      <c r="B24" s="122"/>
-      <c r="C24" s="124"/>
+    <row r="24" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="123"/>
+      <c r="B24" s="125"/>
+      <c r="C24" s="121"/>
       <c r="D24" s="15" t="s">
         <v>126</v>
       </c>
@@ -6899,19 +6902,19 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="120"/>
-      <c r="B25" s="122"/>
-      <c r="C25" s="124"/>
+    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="123"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="121"/>
       <c r="D25" s="15" t="s">
         <v>127</v>
       </c>
       <c r="E25" s="33"/>
     </row>
-    <row r="26" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="120"/>
-      <c r="B26" s="122"/>
-      <c r="C26" s="124"/>
+    <row r="26" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="123"/>
+      <c r="B26" s="125"/>
+      <c r="C26" s="121"/>
       <c r="D26" s="15" t="s">
         <v>128</v>
       </c>
@@ -6919,95 +6922,95 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="120"/>
-      <c r="B27" s="122"/>
-      <c r="C27" s="124"/>
+    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="123"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="121"/>
       <c r="D27" s="15" t="s">
         <v>129</v>
       </c>
       <c r="E27" s="33"/>
     </row>
-    <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="120"/>
-      <c r="B28" s="122"/>
-      <c r="C28" s="124"/>
+    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="123"/>
+      <c r="B28" s="125"/>
+      <c r="C28" s="121"/>
       <c r="D28" s="15" t="s">
         <v>130</v>
       </c>
       <c r="E28" s="33"/>
     </row>
-    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="120"/>
-      <c r="B29" s="122"/>
-      <c r="C29" s="124"/>
+    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="123"/>
+      <c r="B29" s="125"/>
+      <c r="C29" s="121"/>
       <c r="D29" s="15" t="s">
         <v>131</v>
       </c>
       <c r="E29" s="33"/>
     </row>
-    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="120"/>
-      <c r="B30" s="122"/>
-      <c r="C30" s="124"/>
+    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="123"/>
+      <c r="B30" s="125"/>
+      <c r="C30" s="121"/>
       <c r="D30" s="15" t="s">
         <v>132</v>
       </c>
       <c r="E30" s="33"/>
     </row>
-    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="120"/>
-      <c r="B31" s="122"/>
-      <c r="C31" s="124"/>
+    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="123"/>
+      <c r="B31" s="125"/>
+      <c r="C31" s="121"/>
       <c r="D31" s="15" t="s">
         <v>133</v>
       </c>
       <c r="E31" s="33"/>
     </row>
-    <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="120"/>
-      <c r="B32" s="122"/>
-      <c r="C32" s="124"/>
+    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="123"/>
+      <c r="B32" s="125"/>
+      <c r="C32" s="121"/>
       <c r="D32" s="15" t="s">
         <v>134</v>
       </c>
       <c r="E32" s="33"/>
     </row>
-    <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="120"/>
-      <c r="B33" s="122"/>
-      <c r="C33" s="124"/>
+    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="123"/>
+      <c r="B33" s="125"/>
+      <c r="C33" s="121"/>
       <c r="D33" s="15" t="s">
         <v>135</v>
       </c>
       <c r="E33" s="33"/>
     </row>
-    <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="120"/>
-      <c r="B34" s="122"/>
-      <c r="C34" s="124"/>
+    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="123"/>
+      <c r="B34" s="125"/>
+      <c r="C34" s="121"/>
       <c r="D34" s="15" t="s">
         <v>136</v>
       </c>
       <c r="E34" s="33"/>
     </row>
-    <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="116"/>
-      <c r="B35" s="118"/>
-      <c r="C35" s="125"/>
+    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="124"/>
+      <c r="B35" s="126"/>
+      <c r="C35" s="122"/>
       <c r="D35" s="16" t="s">
         <v>137</v>
       </c>
       <c r="E35" s="34"/>
     </row>
-    <row r="36" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="119" t="s">
+    <row r="36" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B36" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" s="123" t="s">
+      <c r="B36" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" s="117" t="s">
         <v>143</v>
       </c>
       <c r="D36" s="14" t="s">
@@ -7017,19 +7020,19 @@
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="120"/>
-      <c r="B37" s="122"/>
-      <c r="C37" s="124"/>
+    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="123"/>
+      <c r="B37" s="125"/>
+      <c r="C37" s="121"/>
       <c r="D37" s="15" t="s">
         <v>145</v>
       </c>
       <c r="E37" s="33"/>
     </row>
-    <row r="38" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="120"/>
-      <c r="B38" s="122"/>
-      <c r="C38" s="124"/>
+    <row r="38" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="123"/>
+      <c r="B38" s="125"/>
+      <c r="C38" s="121"/>
       <c r="D38" s="15" t="s">
         <v>146</v>
       </c>
@@ -7037,141 +7040,141 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="120"/>
-      <c r="B39" s="122"/>
-      <c r="C39" s="124"/>
+    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="123"/>
+      <c r="B39" s="125"/>
+      <c r="C39" s="121"/>
       <c r="D39" s="15" t="s">
         <v>147</v>
       </c>
       <c r="E39" s="33"/>
     </row>
-    <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="116"/>
-      <c r="B40" s="118"/>
-      <c r="C40" s="125"/>
+    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="124"/>
+      <c r="B40" s="126"/>
+      <c r="C40" s="122"/>
       <c r="D40" s="16" t="s">
         <v>148</v>
       </c>
       <c r="E40" s="34"/>
     </row>
-    <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="119" t="s">
+    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C41" s="123" t="s">
+      <c r="B41" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="117" t="s">
         <v>151</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E41" s="129"/>
-    </row>
-    <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="116"/>
-      <c r="B42" s="118"/>
-      <c r="C42" s="125"/>
+      <c r="E41" s="119"/>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="124"/>
+      <c r="B42" s="126"/>
+      <c r="C42" s="122"/>
       <c r="D42" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="E42" s="131"/>
-    </row>
-    <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="119" t="s">
+      <c r="E42" s="130"/>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B43" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C43" s="123" t="s">
+      <c r="B43" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="117" t="s">
         <v>154</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="E43" s="129"/>
-    </row>
-    <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="116"/>
-      <c r="B44" s="118"/>
-      <c r="C44" s="125"/>
+      <c r="E43" s="119"/>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="124"/>
+      <c r="B44" s="126"/>
+      <c r="C44" s="122"/>
       <c r="D44" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="E44" s="131"/>
-    </row>
-    <row r="45" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="119" t="s">
+      <c r="E44" s="130"/>
+    </row>
+    <row r="45" spans="1:5" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B45" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="123" t="s">
+      <c r="B45" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="117" t="s">
         <v>157</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="E45" s="123" t="s">
+      <c r="E45" s="117" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="116"/>
-      <c r="B46" s="118"/>
-      <c r="C46" s="125"/>
+    <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="124"/>
+      <c r="B46" s="126"/>
+      <c r="C46" s="122"/>
       <c r="D46" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="E46" s="125"/>
-    </row>
-    <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="119" t="s">
+      <c r="E46" s="122"/>
+    </row>
+    <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" s="123" t="s">
+      <c r="B47" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="117" t="s">
         <v>161</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E47" s="126"/>
-    </row>
-    <row r="48" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="120"/>
-      <c r="B48" s="122"/>
-      <c r="C48" s="124"/>
+      <c r="E47" s="127"/>
+    </row>
+    <row r="48" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A48" s="123"/>
+      <c r="B48" s="125"/>
+      <c r="C48" s="121"/>
       <c r="D48" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="E48" s="127"/>
-    </row>
-    <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="120"/>
-      <c r="B49" s="122"/>
-      <c r="C49" s="124"/>
+      <c r="E48" s="129"/>
+    </row>
+    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="123"/>
+      <c r="B49" s="125"/>
+      <c r="C49" s="121"/>
       <c r="D49" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="E49" s="127"/>
-    </row>
-    <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="116"/>
-      <c r="B50" s="118"/>
-      <c r="C50" s="125"/>
+      <c r="E49" s="129"/>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="124"/>
+      <c r="B50" s="126"/>
+      <c r="C50" s="122"/>
       <c r="D50" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="E50" s="114"/>
-    </row>
-    <row r="51" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="E50" s="128"/>
+    </row>
+    <row r="51" spans="1:5" ht="63" x14ac:dyDescent="0.25">
       <c r="A51" s="132" t="s">
         <v>90</v>
       </c>
@@ -7188,14 +7191,14 @@
         <v>168</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="133"/>
       <c r="B52" s="136"/>
       <c r="C52" s="139"/>
       <c r="D52" s="37"/>
       <c r="E52" s="37"/>
     </row>
-    <row r="53" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="63" x14ac:dyDescent="0.25">
       <c r="A53" s="134"/>
       <c r="B53" s="137"/>
       <c r="C53" s="140"/>
@@ -7206,7 +7209,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="40" t="s">
         <v>90</v>
       </c>
@@ -7221,14 +7224,14 @@
       </c>
       <c r="E54" s="42"/>
     </row>
-    <row r="55" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="119" t="s">
+    <row r="55" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B55" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C55" s="123" t="s">
+      <c r="B55" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C55" s="117" t="s">
         <v>172</v>
       </c>
       <c r="D55" s="14" t="s">
@@ -7238,19 +7241,19 @@
         <v>177</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="120"/>
-      <c r="B56" s="122"/>
-      <c r="C56" s="124"/>
+    <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="123"/>
+      <c r="B56" s="125"/>
+      <c r="C56" s="121"/>
       <c r="D56" s="15" t="s">
         <v>174</v>
       </c>
       <c r="E56" s="33"/>
     </row>
-    <row r="57" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="120"/>
-      <c r="B57" s="122"/>
-      <c r="C57" s="124"/>
+    <row r="57" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="123"/>
+      <c r="B57" s="125"/>
+      <c r="C57" s="121"/>
       <c r="D57" s="15" t="s">
         <v>175</v>
       </c>
@@ -7258,67 +7261,67 @@
         <v>178</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="116"/>
-      <c r="B58" s="118"/>
-      <c r="C58" s="125"/>
+    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="124"/>
+      <c r="B58" s="126"/>
+      <c r="C58" s="122"/>
       <c r="D58" s="16" t="s">
         <v>176</v>
       </c>
       <c r="E58" s="34"/>
     </row>
-    <row r="59" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="119" t="s">
+    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B59" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C59" s="123" t="s">
+      <c r="B59" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" s="117" t="s">
         <v>179</v>
       </c>
       <c r="D59" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="E59" s="123" t="s">
+      <c r="E59" s="117" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="120"/>
-      <c r="B60" s="122"/>
-      <c r="C60" s="124"/>
+    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="123"/>
+      <c r="B60" s="125"/>
+      <c r="C60" s="121"/>
       <c r="D60" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E60" s="124"/>
-    </row>
-    <row r="61" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="120"/>
-      <c r="B61" s="122"/>
-      <c r="C61" s="124"/>
+      <c r="E60" s="121"/>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="123"/>
+      <c r="B61" s="125"/>
+      <c r="C61" s="121"/>
       <c r="D61" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="E61" s="124"/>
-    </row>
-    <row r="62" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="116"/>
-      <c r="B62" s="118"/>
-      <c r="C62" s="125"/>
+      <c r="E61" s="121"/>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="124"/>
+      <c r="B62" s="126"/>
+      <c r="C62" s="122"/>
       <c r="D62" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="E62" s="125"/>
-    </row>
-    <row r="63" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="119" t="s">
+      <c r="E62" s="122"/>
+    </row>
+    <row r="63" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A63" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B63" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C63" s="123" t="s">
+      <c r="B63" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C63" s="117" t="s">
         <v>184</v>
       </c>
       <c r="D63" s="14" t="s">
@@ -7328,19 +7331,19 @@
         <v>193</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="120"/>
-      <c r="B64" s="122"/>
-      <c r="C64" s="124"/>
+    <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="123"/>
+      <c r="B64" s="125"/>
+      <c r="C64" s="121"/>
       <c r="D64" s="15" t="s">
         <v>186</v>
       </c>
       <c r="E64" s="33"/>
     </row>
-    <row r="65" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="120"/>
-      <c r="B65" s="122"/>
-      <c r="C65" s="124"/>
+    <row r="65" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="123"/>
+      <c r="B65" s="125"/>
+      <c r="C65" s="121"/>
       <c r="D65" s="15" t="s">
         <v>187</v>
       </c>
@@ -7348,19 +7351,19 @@
         <v>194</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="120"/>
-      <c r="B66" s="122"/>
-      <c r="C66" s="124"/>
+    <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="123"/>
+      <c r="B66" s="125"/>
+      <c r="C66" s="121"/>
       <c r="D66" s="15" t="s">
         <v>188</v>
       </c>
       <c r="E66" s="33"/>
     </row>
-    <row r="67" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="120"/>
-      <c r="B67" s="122"/>
-      <c r="C67" s="124"/>
+    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="123"/>
+      <c r="B67" s="125"/>
+      <c r="C67" s="121"/>
       <c r="D67" s="15" t="s">
         <v>189</v>
       </c>
@@ -7368,85 +7371,85 @@
         <v>195</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="120"/>
-      <c r="B68" s="122"/>
-      <c r="C68" s="124"/>
+    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="123"/>
+      <c r="B68" s="125"/>
+      <c r="C68" s="121"/>
       <c r="D68" s="15" t="s">
         <v>190</v>
       </c>
       <c r="E68" s="33"/>
     </row>
-    <row r="69" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="120"/>
-      <c r="B69" s="122"/>
-      <c r="C69" s="124"/>
+    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="123"/>
+      <c r="B69" s="125"/>
+      <c r="C69" s="121"/>
       <c r="D69" s="15" t="s">
         <v>191</v>
       </c>
       <c r="E69" s="33"/>
     </row>
-    <row r="70" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="116"/>
-      <c r="B70" s="118"/>
-      <c r="C70" s="125"/>
+    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="124"/>
+      <c r="B70" s="126"/>
+      <c r="C70" s="122"/>
       <c r="D70" s="16" t="s">
         <v>192</v>
       </c>
       <c r="E70" s="34"/>
     </row>
-    <row r="71" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A71" s="119" t="s">
+    <row r="71" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B71" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C71" s="123" t="s">
+      <c r="B71" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C71" s="117" t="s">
         <v>196</v>
       </c>
       <c r="D71" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="E71" s="123" t="s">
+      <c r="E71" s="117" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="120"/>
-      <c r="B72" s="122"/>
-      <c r="C72" s="124"/>
+    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="123"/>
+      <c r="B72" s="125"/>
+      <c r="C72" s="121"/>
       <c r="D72" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="E72" s="124"/>
-    </row>
-    <row r="73" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="120"/>
-      <c r="B73" s="122"/>
-      <c r="C73" s="124"/>
+      <c r="E72" s="121"/>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="123"/>
+      <c r="B73" s="125"/>
+      <c r="C73" s="121"/>
       <c r="D73" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="E73" s="124"/>
-    </row>
-    <row r="74" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="116"/>
-      <c r="B74" s="118"/>
-      <c r="C74" s="125"/>
+      <c r="E73" s="121"/>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="124"/>
+      <c r="B74" s="126"/>
+      <c r="C74" s="122"/>
       <c r="D74" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="E74" s="125"/>
-    </row>
-    <row r="75" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="119" t="s">
+      <c r="E74" s="122"/>
+    </row>
+    <row r="75" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B75" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C75" s="123" t="s">
+      <c r="B75" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C75" s="117" t="s">
         <v>202</v>
       </c>
       <c r="D75" s="43" t="s">
@@ -7456,10 +7459,10 @@
         <v>207</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="120"/>
-      <c r="B76" s="122"/>
-      <c r="C76" s="124"/>
+    <row r="76" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A76" s="123"/>
+      <c r="B76" s="125"/>
+      <c r="C76" s="121"/>
       <c r="D76" s="15" t="s">
         <v>204</v>
       </c>
@@ -7467,32 +7470,32 @@
         <v>208</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="120"/>
-      <c r="B77" s="122"/>
-      <c r="C77" s="124"/>
+    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="123"/>
+      <c r="B77" s="125"/>
+      <c r="C77" s="121"/>
       <c r="D77" s="15" t="s">
         <v>205</v>
       </c>
       <c r="E77" s="33"/>
     </row>
-    <row r="78" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="116"/>
-      <c r="B78" s="118"/>
-      <c r="C78" s="125"/>
+    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="124"/>
+      <c r="B78" s="126"/>
+      <c r="C78" s="122"/>
       <c r="D78" s="16" t="s">
         <v>206</v>
       </c>
       <c r="E78" s="34"/>
     </row>
-    <row r="79" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A79" s="119" t="s">
+    <row r="79" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B79" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C79" s="123" t="s">
+      <c r="B79" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C79" s="117" t="s">
         <v>209</v>
       </c>
       <c r="D79" s="14" t="s">
@@ -7502,19 +7505,19 @@
         <v>216</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="120"/>
-      <c r="B80" s="122"/>
-      <c r="C80" s="124"/>
+    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="123"/>
+      <c r="B80" s="125"/>
+      <c r="C80" s="121"/>
       <c r="D80" s="15" t="s">
         <v>211</v>
       </c>
       <c r="E80" s="33"/>
     </row>
-    <row r="81" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A81" s="120"/>
-      <c r="B81" s="122"/>
-      <c r="C81" s="124"/>
+    <row r="81" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A81" s="123"/>
+      <c r="B81" s="125"/>
+      <c r="C81" s="121"/>
       <c r="D81" s="15" t="s">
         <v>212</v>
       </c>
@@ -7522,34 +7525,34 @@
         <v>217</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A82" s="120"/>
-      <c r="B82" s="122"/>
-      <c r="C82" s="124"/>
+    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="123"/>
+      <c r="B82" s="125"/>
+      <c r="C82" s="121"/>
       <c r="D82" s="15" t="s">
         <v>213</v>
       </c>
       <c r="E82" s="33"/>
     </row>
-    <row r="83" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A83" s="120"/>
-      <c r="B83" s="122"/>
-      <c r="C83" s="124"/>
+    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="123"/>
+      <c r="B83" s="125"/>
+      <c r="C83" s="121"/>
       <c r="D83" s="15" t="s">
         <v>214</v>
       </c>
       <c r="E83" s="33"/>
     </row>
-    <row r="84" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A84" s="116"/>
-      <c r="B84" s="118"/>
-      <c r="C84" s="125"/>
+    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="124"/>
+      <c r="B84" s="126"/>
+      <c r="C84" s="122"/>
       <c r="D84" s="16" t="s">
         <v>215</v>
       </c>
       <c r="E84" s="34"/>
     </row>
-    <row r="85" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A85" s="44" t="s">
         <v>90</v>
       </c>
@@ -7566,7 +7569,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A86" s="44" t="s">
         <v>90</v>
       </c>
@@ -7581,58 +7584,58 @@
       </c>
       <c r="E86" s="42"/>
     </row>
-    <row r="87" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A87" s="119" t="s">
+    <row r="87" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="B87" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C87" s="123" t="s">
+      <c r="B87" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C87" s="117" t="s">
         <v>222</v>
       </c>
       <c r="D87" s="43" t="s">
         <v>223</v>
       </c>
-      <c r="E87" s="126"/>
-    </row>
-    <row r="88" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A88" s="120"/>
-      <c r="B88" s="122"/>
-      <c r="C88" s="124"/>
+      <c r="E87" s="127"/>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="123"/>
+      <c r="B88" s="125"/>
+      <c r="C88" s="121"/>
       <c r="D88" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="E88" s="127"/>
-    </row>
-    <row r="89" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A89" s="120"/>
-      <c r="B89" s="122"/>
-      <c r="C89" s="124"/>
+      <c r="E88" s="129"/>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="123"/>
+      <c r="B89" s="125"/>
+      <c r="C89" s="121"/>
       <c r="D89" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="E89" s="127"/>
-    </row>
-    <row r="90" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A90" s="120"/>
-      <c r="B90" s="122"/>
-      <c r="C90" s="124"/>
+      <c r="E89" s="129"/>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A90" s="123"/>
+      <c r="B90" s="125"/>
+      <c r="C90" s="121"/>
       <c r="D90" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="E90" s="127"/>
-    </row>
-    <row r="91" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A91" s="116"/>
-      <c r="B91" s="118"/>
-      <c r="C91" s="125"/>
+      <c r="E90" s="129"/>
+    </row>
+    <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A91" s="124"/>
+      <c r="B91" s="126"/>
+      <c r="C91" s="122"/>
       <c r="D91" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="E91" s="114"/>
-    </row>
-    <row r="92" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E91" s="128"/>
+    </row>
+    <row r="92" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A92" s="44" t="s">
         <v>90</v>
       </c>
@@ -7649,7 +7652,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" ht="63" x14ac:dyDescent="0.25">
       <c r="A93" s="44" t="s">
         <v>90</v>
       </c>
@@ -7666,7 +7669,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="44" t="s">
         <v>234</v>
       </c>
@@ -7681,90 +7684,90 @@
       </c>
       <c r="E94" s="46"/>
     </row>
-    <row r="95" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A95" s="119" t="s">
+    <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="113" t="s">
         <v>234</v>
       </c>
-      <c r="B95" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C95" s="123" t="s">
+      <c r="B95" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C95" s="117" t="s">
         <v>237</v>
       </c>
       <c r="D95" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="E95" s="126"/>
-    </row>
-    <row r="96" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A96" s="116"/>
-      <c r="B96" s="118"/>
-      <c r="C96" s="125"/>
+      <c r="E95" s="127"/>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A96" s="124"/>
+      <c r="B96" s="126"/>
+      <c r="C96" s="122"/>
       <c r="D96" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="E96" s="114"/>
-    </row>
-    <row r="97" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A97" s="119" t="s">
+      <c r="E96" s="128"/>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="113" t="s">
         <v>234</v>
       </c>
-      <c r="B97" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C97" s="123" t="s">
+      <c r="B97" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C97" s="117" t="s">
         <v>240</v>
       </c>
       <c r="D97" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="E97" s="126"/>
-    </row>
-    <row r="98" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A98" s="116"/>
-      <c r="B98" s="118"/>
-      <c r="C98" s="125"/>
+      <c r="E97" s="127"/>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="124"/>
+      <c r="B98" s="126"/>
+      <c r="C98" s="122"/>
       <c r="D98" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="E98" s="114"/>
-    </row>
-    <row r="99" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A99" s="119" t="s">
+      <c r="E98" s="128"/>
+    </row>
+    <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="113" t="s">
         <v>234</v>
       </c>
-      <c r="B99" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C99" s="123" t="s">
+      <c r="B99" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C99" s="117" t="s">
         <v>242</v>
       </c>
       <c r="D99" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="E99" s="123" t="s">
+      <c r="E99" s="117" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A100" s="120"/>
-      <c r="B100" s="122"/>
-      <c r="C100" s="124"/>
+    <row r="100" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="123"/>
+      <c r="B100" s="125"/>
+      <c r="C100" s="121"/>
       <c r="D100" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="E100" s="124"/>
-    </row>
-    <row r="101" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A101" s="116"/>
-      <c r="B101" s="118"/>
-      <c r="C101" s="125"/>
+      <c r="E100" s="121"/>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="124"/>
+      <c r="B101" s="126"/>
+      <c r="C101" s="122"/>
       <c r="D101" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="E101" s="125"/>
-    </row>
-    <row r="102" spans="1:5" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E101" s="122"/>
+    </row>
+    <row r="102" spans="1:5" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="47" t="s">
         <v>234</v>
       </c>
@@ -7781,81 +7784,161 @@
         <v>247</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="119" t="s">
+    <row r="103" spans="1:5" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="113" t="s">
         <v>234</v>
       </c>
-      <c r="B103" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C103" s="123" t="s">
+      <c r="B103" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C103" s="117" t="s">
         <v>248</v>
       </c>
       <c r="D103" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="E103" s="123" t="s">
+      <c r="E103" s="117" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="120"/>
-      <c r="B104" s="122"/>
-      <c r="C104" s="124"/>
+    <row r="104" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="123"/>
+      <c r="B104" s="125"/>
+      <c r="C104" s="121"/>
       <c r="D104" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E104" s="124"/>
-    </row>
-    <row r="105" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="116"/>
-      <c r="B105" s="118"/>
-      <c r="C105" s="125"/>
+      <c r="E104" s="121"/>
+    </row>
+    <row r="105" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="124"/>
+      <c r="B105" s="126"/>
+      <c r="C105" s="122"/>
       <c r="D105" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="E105" s="125"/>
-    </row>
-    <row r="106" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A106" s="119" t="s">
+      <c r="E105" s="122"/>
+    </row>
+    <row r="106" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="113" t="s">
         <v>234</v>
       </c>
-      <c r="B106" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C106" s="123" t="s">
+      <c r="B106" s="115" t="s">
+        <v>91</v>
+      </c>
+      <c r="C106" s="117" t="s">
         <v>251</v>
       </c>
       <c r="D106" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="E106" s="129"/>
-    </row>
-    <row r="107" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="141"/>
-      <c r="B107" s="142"/>
-      <c r="C107" s="143"/>
+      <c r="E106" s="119"/>
+    </row>
+    <row r="107" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="114"/>
+      <c r="B107" s="116"/>
+      <c r="C107" s="118"/>
       <c r="D107" s="50" t="s">
         <v>224</v>
       </c>
-      <c r="E107" s="144"/>
-    </row>
-    <row r="108" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A108" s="119"/>
-      <c r="B108" s="121"/>
-      <c r="C108" s="123"/>
+      <c r="E107" s="120"/>
+    </row>
+    <row r="108" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="113"/>
+      <c r="B108" s="115"/>
+      <c r="C108" s="117"/>
       <c r="D108" s="14"/>
-      <c r="E108" s="129"/>
-    </row>
-    <row r="109" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="141"/>
-      <c r="B109" s="142"/>
-      <c r="C109" s="143"/>
+      <c r="E108" s="119"/>
+    </row>
+    <row r="109" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="114"/>
+      <c r="B109" s="116"/>
+      <c r="C109" s="118"/>
       <c r="D109" s="50"/>
-      <c r="E109" s="144"/>
+      <c r="E109" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="96">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="E95:E96"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="C75:C78"/>
+    <mergeCell ref="A79:A84"/>
+    <mergeCell ref="C79:C84"/>
+    <mergeCell ref="A87:A91"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="C87:C91"/>
+    <mergeCell ref="E87:E91"/>
+    <mergeCell ref="B79:B84"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="C12:C17"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="C36:C40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="A36:A40"/>
+    <mergeCell ref="A21:A35"/>
+    <mergeCell ref="B21:B35"/>
+    <mergeCell ref="C21:C35"/>
+    <mergeCell ref="B36:B40"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="E47:E50"/>
+    <mergeCell ref="E59:E62"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="C55:C58"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="E99:E101"/>
+    <mergeCell ref="C103:C105"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="A63:A70"/>
+    <mergeCell ref="B63:B70"/>
+    <mergeCell ref="C63:C70"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:C109"/>
@@ -7872,86 +7955,6 @@
     <mergeCell ref="A99:A101"/>
     <mergeCell ref="B99:B101"/>
     <mergeCell ref="C99:C101"/>
-    <mergeCell ref="E99:E101"/>
-    <mergeCell ref="C103:C105"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="A63:A70"/>
-    <mergeCell ref="B63:B70"/>
-    <mergeCell ref="C63:C70"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="C71:C74"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="B47:B50"/>
-    <mergeCell ref="C47:C50"/>
-    <mergeCell ref="E47:E50"/>
-    <mergeCell ref="E59:E62"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="C55:C58"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="B59:B62"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="A21:A35"/>
-    <mergeCell ref="B21:B35"/>
-    <mergeCell ref="C21:C35"/>
-    <mergeCell ref="B36:B40"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="C36:C40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="A36:A40"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="C12:C17"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="E95:E96"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="B75:B78"/>
-    <mergeCell ref="C75:C78"/>
-    <mergeCell ref="A79:A84"/>
-    <mergeCell ref="C79:C84"/>
-    <mergeCell ref="A87:A91"/>
-    <mergeCell ref="B87:B91"/>
-    <mergeCell ref="C87:C91"/>
-    <mergeCell ref="E87:E91"/>
-    <mergeCell ref="B79:B84"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="C2:C3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7960,16 +7963,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0235A7-9553-43A7-84D6-59D2907400E9}">
   <dimension ref="A1:E84"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.21875" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="34.77734375" customWidth="1"/>
-    <col min="4" max="4" width="37.5546875" customWidth="1"/>
-    <col min="5" max="5" width="66.77734375" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="4" max="4" width="37.5703125" customWidth="1"/>
+    <col min="5" max="5" width="66.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
@@ -7986,7 +7989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="81" t="s">
         <v>90</v>
       </c>
@@ -8003,7 +8006,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="82" t="s">
         <v>90</v>
       </c>
@@ -8018,7 +8021,7 @@
       </c>
       <c r="E3" s="56"/>
     </row>
-    <row r="4" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A4" s="82" t="s">
         <v>90</v>
       </c>
@@ -8035,7 +8038,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="82" t="s">
         <v>90</v>
       </c>
@@ -8050,7 +8053,7 @@
       </c>
       <c r="E5" s="56"/>
     </row>
-    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="83" t="s">
         <v>90</v>
       </c>
@@ -8065,7 +8068,7 @@
       </c>
       <c r="E6" s="68"/>
     </row>
-    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="82" t="s">
         <v>90</v>
       </c>
@@ -8080,7 +8083,7 @@
       </c>
       <c r="E7" s="56"/>
     </row>
-    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="83" t="s">
         <v>90</v>
       </c>
@@ -8095,7 +8098,7 @@
       </c>
       <c r="E8" s="68"/>
     </row>
-    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="83" t="s">
         <v>90</v>
       </c>
@@ -8110,7 +8113,7 @@
       </c>
       <c r="E9" s="68"/>
     </row>
-    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="82" t="s">
         <v>90</v>
       </c>
@@ -8125,7 +8128,7 @@
       </c>
       <c r="E10" s="56"/>
     </row>
-    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="83" t="s">
         <v>90</v>
       </c>
@@ -8140,7 +8143,7 @@
       </c>
       <c r="E11" s="68"/>
     </row>
-    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="82" t="s">
         <v>90</v>
       </c>
@@ -8155,7 +8158,7 @@
       </c>
       <c r="E12" s="56"/>
     </row>
-    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="82" t="s">
         <v>90</v>
       </c>
@@ -8172,7 +8175,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="82" t="s">
         <v>90</v>
       </c>
@@ -8187,7 +8190,7 @@
       </c>
       <c r="E14" s="56"/>
     </row>
-    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="83" t="s">
         <v>90</v>
       </c>
@@ -8202,7 +8205,7 @@
       </c>
       <c r="E15" s="68"/>
     </row>
-    <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="82" t="s">
         <v>90</v>
       </c>
@@ -8219,7 +8222,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="82" t="s">
         <v>90</v>
       </c>
@@ -8234,7 +8237,7 @@
       </c>
       <c r="E17" s="56"/>
     </row>
-    <row r="18" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" s="82" t="s">
         <v>90</v>
       </c>
@@ -8251,7 +8254,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="82" t="s">
         <v>90</v>
       </c>
@@ -8268,7 +8271,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="82" t="s">
         <v>90</v>
       </c>
@@ -8283,7 +8286,7 @@
       </c>
       <c r="E20" s="56"/>
     </row>
-    <row r="21" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="82" t="s">
         <v>90</v>
       </c>
@@ -8298,7 +8301,7 @@
       </c>
       <c r="E21" s="79"/>
     </row>
-    <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="82" t="s">
         <v>90</v>
       </c>
@@ -8313,7 +8316,7 @@
       </c>
       <c r="E22" s="57"/>
     </row>
-    <row r="23" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A23" s="82" t="s">
         <v>90</v>
       </c>
@@ -8328,7 +8331,7 @@
       </c>
       <c r="E23" s="56"/>
     </row>
-    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="82" t="s">
         <v>90</v>
       </c>
@@ -8343,7 +8346,7 @@
       </c>
       <c r="E24" s="56"/>
     </row>
-    <row r="25" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="82" t="s">
         <v>90</v>
       </c>
@@ -8358,7 +8361,7 @@
       </c>
       <c r="E25" s="56"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="82" t="s">
         <v>90</v>
       </c>
@@ -8373,7 +8376,7 @@
       </c>
       <c r="E26" s="56"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="82" t="s">
         <v>90</v>
       </c>
@@ -8388,7 +8391,7 @@
       </c>
       <c r="E27" s="56"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="82" t="s">
         <v>90</v>
       </c>
@@ -8403,7 +8406,7 @@
       </c>
       <c r="E28" s="57"/>
     </row>
-    <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="82" t="s">
         <v>90</v>
       </c>
@@ -8418,7 +8421,7 @@
       </c>
       <c r="E29" s="56"/>
     </row>
-    <row r="30" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A30" s="82" t="s">
         <v>90</v>
       </c>
@@ -8435,7 +8438,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="82" t="s">
         <v>90</v>
       </c>
@@ -8450,7 +8453,7 @@
       </c>
       <c r="E31" s="56"/>
     </row>
-    <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="82" t="s">
         <v>90</v>
       </c>
@@ -8465,7 +8468,7 @@
       </c>
       <c r="E32" s="57"/>
     </row>
-    <row r="33" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A33" s="82" t="s">
         <v>90</v>
       </c>
@@ -8482,7 +8485,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="82" t="s">
         <v>90</v>
       </c>
@@ -8497,7 +8500,7 @@
       </c>
       <c r="E34" s="57"/>
     </row>
-    <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="82" t="s">
         <v>90</v>
       </c>
@@ -8512,7 +8515,7 @@
       </c>
       <c r="E35" s="57"/>
     </row>
-    <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="83" t="s">
         <v>90</v>
       </c>
@@ -8527,7 +8530,7 @@
       </c>
       <c r="E36" s="68"/>
     </row>
-    <row r="37" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="82" t="s">
         <v>90</v>
       </c>
@@ -8542,7 +8545,7 @@
       </c>
       <c r="E37" s="57"/>
     </row>
-    <row r="38" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="83" t="s">
         <v>90</v>
       </c>
@@ -8557,7 +8560,7 @@
       </c>
       <c r="E38" s="68"/>
     </row>
-    <row r="39" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="82" t="s">
         <v>90</v>
       </c>
@@ -8572,7 +8575,7 @@
       </c>
       <c r="E39" s="57"/>
     </row>
-    <row r="40" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A40" s="82" t="s">
         <v>90</v>
       </c>
@@ -8589,7 +8592,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="82" t="s">
         <v>90</v>
       </c>
@@ -8606,7 +8609,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A42" s="83" t="s">
         <v>90</v>
       </c>
@@ -8621,7 +8624,7 @@
       </c>
       <c r="E42" s="68"/>
     </row>
-    <row r="43" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A43" s="82" t="s">
         <v>90</v>
       </c>
@@ -8638,7 +8641,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="82" t="s">
         <v>90</v>
       </c>
@@ -8653,7 +8656,7 @@
       </c>
       <c r="E44" s="56"/>
     </row>
-    <row r="45" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A45" s="83" t="s">
         <v>234</v>
       </c>
@@ -8668,7 +8671,7 @@
       </c>
       <c r="E45" s="68"/>
     </row>
-    <row r="46" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A46" s="83" t="s">
         <v>234</v>
       </c>
@@ -8683,7 +8686,7 @@
       </c>
       <c r="E46" s="68"/>
     </row>
-    <row r="47" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A47" s="83" t="s">
         <v>234</v>
       </c>
@@ -8698,7 +8701,7 @@
       </c>
       <c r="E47" s="68"/>
     </row>
-    <row r="48" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A48" s="83" t="s">
         <v>234</v>
       </c>
@@ -8713,7 +8716,7 @@
       </c>
       <c r="E48" s="68"/>
     </row>
-    <row r="49" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="82" t="s">
         <v>234</v>
       </c>
@@ -8728,7 +8731,7 @@
       </c>
       <c r="E49" s="56"/>
     </row>
-    <row r="50" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="82" t="s">
         <v>234</v>
       </c>
@@ -8743,7 +8746,7 @@
       </c>
       <c r="E50" s="57"/>
     </row>
-    <row r="51" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="82" t="s">
         <v>234</v>
       </c>
@@ -8758,7 +8761,7 @@
       </c>
       <c r="E51" s="57"/>
     </row>
-    <row r="52" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A52" s="82" t="s">
         <v>234</v>
       </c>
@@ -8773,7 +8776,7 @@
       </c>
       <c r="E52" s="57"/>
     </row>
-    <row r="53" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A53" s="82" t="s">
         <v>234</v>
       </c>
@@ -8788,7 +8791,7 @@
       </c>
       <c r="E53" s="57"/>
     </row>
-    <row r="54" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A54" s="82" t="s">
         <v>234</v>
       </c>
@@ -8803,7 +8806,7 @@
       </c>
       <c r="E54" s="57"/>
     </row>
-    <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="82" t="s">
         <v>234</v>
       </c>
@@ -8818,7 +8821,7 @@
       </c>
       <c r="E55" s="57"/>
     </row>
-    <row r="56" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="82" t="s">
         <v>234</v>
       </c>
@@ -8833,7 +8836,7 @@
       </c>
       <c r="E56" s="56"/>
     </row>
-    <row r="57" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A57" s="83" t="s">
         <v>234</v>
       </c>
@@ -8848,7 +8851,7 @@
       </c>
       <c r="E57" s="68"/>
     </row>
-    <row r="58" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A58" s="83" t="s">
         <v>234</v>
       </c>
@@ -8863,7 +8866,7 @@
       </c>
       <c r="E58" s="68"/>
     </row>
-    <row r="59" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A59" s="83" t="s">
         <v>234</v>
       </c>
@@ -8878,7 +8881,7 @@
       </c>
       <c r="E59" s="68"/>
     </row>
-    <row r="60" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="83" t="s">
         <v>234</v>
       </c>
@@ -8895,7 +8898,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="82" t="s">
         <v>234</v>
       </c>
@@ -8910,7 +8913,7 @@
       </c>
       <c r="E61" s="56"/>
     </row>
-    <row r="62" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="82" t="s">
         <v>234</v>
       </c>
@@ -8925,7 +8928,7 @@
       </c>
       <c r="E62" s="57"/>
     </row>
-    <row r="63" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="83" t="s">
         <v>234</v>
       </c>
@@ -8940,7 +8943,7 @@
       </c>
       <c r="E63" s="68"/>
     </row>
-    <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A64" s="83" t="s">
         <v>234</v>
       </c>
@@ -8955,7 +8958,7 @@
       </c>
       <c r="E64" s="68"/>
     </row>
-    <row r="65" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A65" s="83" t="s">
         <v>234</v>
       </c>
@@ -8970,7 +8973,7 @@
       </c>
       <c r="E65" s="80"/>
     </row>
-    <row r="66" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A66" s="83" t="s">
         <v>234</v>
       </c>
@@ -8985,7 +8988,7 @@
       </c>
       <c r="E66" s="80"/>
     </row>
-    <row r="67" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A67" s="83" t="s">
         <v>234</v>
       </c>
@@ -9000,7 +9003,7 @@
       </c>
       <c r="E67" s="80"/>
     </row>
-    <row r="68" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="82" t="s">
         <v>234</v>
       </c>
@@ -9015,7 +9018,7 @@
       </c>
       <c r="E68" s="57"/>
     </row>
-    <row r="69" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A69" s="82" t="s">
         <v>234</v>
       </c>
@@ -9030,7 +9033,7 @@
       </c>
       <c r="E69" s="57"/>
     </row>
-    <row r="70" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="82" t="s">
         <v>234</v>
       </c>
@@ -9045,7 +9048,7 @@
       </c>
       <c r="E70" s="57"/>
     </row>
-    <row r="71" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="82" t="s">
         <v>234</v>
       </c>
@@ -9060,7 +9063,7 @@
       </c>
       <c r="E71" s="57"/>
     </row>
-    <row r="72" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A72" s="83" t="s">
         <v>234</v>
       </c>
@@ -9075,7 +9078,7 @@
       </c>
       <c r="E72" s="80"/>
     </row>
-    <row r="73" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A73" s="83" t="s">
         <v>234</v>
       </c>
@@ -9090,7 +9093,7 @@
       </c>
       <c r="E73" s="80"/>
     </row>
-    <row r="74" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A74" s="83" t="s">
         <v>234</v>
       </c>
@@ -9105,7 +9108,7 @@
       </c>
       <c r="E74" s="68"/>
     </row>
-    <row r="75" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="82" t="s">
         <v>234</v>
       </c>
@@ -9120,7 +9123,7 @@
       </c>
       <c r="E75" s="57"/>
     </row>
-    <row r="76" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="83" t="s">
         <v>234</v>
       </c>
@@ -9135,7 +9138,7 @@
       </c>
       <c r="E76" s="80"/>
     </row>
-    <row r="77" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="82" t="s">
         <v>234</v>
       </c>
@@ -9150,7 +9153,7 @@
       </c>
       <c r="E77" s="57"/>
     </row>
-    <row r="78" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="83" t="s">
         <v>234</v>
       </c>
@@ -9165,7 +9168,7 @@
       </c>
       <c r="E78" s="68"/>
     </row>
-    <row r="79" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A79" s="82" t="s">
         <v>234</v>
       </c>
@@ -9180,7 +9183,7 @@
       </c>
       <c r="E79" s="57"/>
     </row>
-    <row r="80" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="82" t="s">
         <v>234</v>
       </c>
@@ -9195,7 +9198,7 @@
       </c>
       <c r="E80" s="57"/>
     </row>
-    <row r="81" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="82" t="s">
         <v>234</v>
       </c>
@@ -9210,7 +9213,7 @@
       </c>
       <c r="E81" s="57"/>
     </row>
-    <row r="82" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="82" t="s">
         <v>234</v>
       </c>
@@ -9225,7 +9228,7 @@
       </c>
       <c r="E82" s="57"/>
     </row>
-    <row r="83" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="82" t="s">
         <v>234</v>
       </c>
@@ -9240,7 +9243,7 @@
       </c>
       <c r="E83" s="56"/>
     </row>
-    <row r="84" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="84" t="s">
         <v>234</v>
       </c>
@@ -9263,15 +9266,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FA0C968-D62F-447C-B9A9-BD95ECAA121D}">
   <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="54.6640625" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" customWidth="1"/>
-    <col min="4" max="4" width="53.88671875" customWidth="1"/>
-    <col min="5" max="5" width="57.44140625" customWidth="1"/>
+    <col min="2" max="2" width="54.7109375" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" customWidth="1"/>
+    <col min="4" max="4" width="53.85546875" customWidth="1"/>
+    <col min="5" max="5" width="57.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
@@ -9288,7 +9291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="90" t="s">
         <v>277</v>
       </c>
@@ -9303,7 +9306,7 @@
       </c>
       <c r="E2" s="92"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="93" t="s">
         <v>277</v>
       </c>
@@ -9318,7 +9321,7 @@
       </c>
       <c r="E3" s="88"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="93" t="s">
         <v>277</v>
       </c>
@@ -9333,7 +9336,7 @@
       </c>
       <c r="E4" s="88"/>
     </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="94" t="s">
         <v>277</v>
       </c>
@@ -9348,7 +9351,7 @@
       </c>
       <c r="E5" s="79"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="93" t="s">
         <v>277</v>
       </c>
@@ -9363,7 +9366,7 @@
       </c>
       <c r="E6" s="88"/>
     </row>
-    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="93" t="s">
         <v>277</v>
       </c>
@@ -9378,7 +9381,7 @@
       </c>
       <c r="E7" s="88"/>
     </row>
-    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="94" t="s">
         <v>277</v>
       </c>
@@ -9393,7 +9396,7 @@
       </c>
       <c r="E8" s="79"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="94" t="s">
         <v>277</v>
       </c>
@@ -9408,7 +9411,7 @@
       </c>
       <c r="E9" s="79"/>
     </row>
-    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="94" t="s">
         <v>277</v>
       </c>
@@ -9423,7 +9426,7 @@
       </c>
       <c r="E10" s="79"/>
     </row>
-    <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="94" t="s">
         <v>277</v>
       </c>
@@ -9438,7 +9441,7 @@
       </c>
       <c r="E11" s="79"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="93" t="s">
         <v>277</v>
       </c>
@@ -9453,7 +9456,7 @@
       </c>
       <c r="E12" s="88"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="94" t="s">
         <v>277</v>
       </c>
@@ -9468,7 +9471,7 @@
       </c>
       <c r="E13" s="79"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="93" t="s">
         <v>277</v>
       </c>
@@ -9483,7 +9486,7 @@
       </c>
       <c r="E14" s="88"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="93" t="s">
         <v>277</v>
       </c>
@@ -9498,7 +9501,7 @@
       </c>
       <c r="E15" s="88"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="93" t="s">
         <v>277</v>
       </c>
@@ -9513,7 +9516,7 @@
       </c>
       <c r="E16" s="88"/>
     </row>
-    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="94" t="s">
         <v>277</v>
       </c>
@@ -9528,7 +9531,7 @@
       </c>
       <c r="E17" s="79"/>
     </row>
-    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="94" t="s">
         <v>277</v>
       </c>
@@ -9543,7 +9546,7 @@
       </c>
       <c r="E18" s="79"/>
     </row>
-    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="94" t="s">
         <v>277</v>
       </c>
@@ -9558,7 +9561,7 @@
       </c>
       <c r="E19" s="79"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="93" t="s">
         <v>277</v>
       </c>
@@ -9573,7 +9576,7 @@
       </c>
       <c r="E20" s="88"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="93" t="s">
         <v>277</v>
       </c>
@@ -9588,7 +9591,7 @@
       </c>
       <c r="E21" s="88"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="93" t="s">
         <v>277</v>
       </c>
@@ -9603,7 +9606,7 @@
       </c>
       <c r="E22" s="88"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="93" t="s">
         <v>277</v>
       </c>
@@ -9618,7 +9621,7 @@
       </c>
       <c r="E23" s="88"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="93" t="s">
         <v>277</v>
       </c>
@@ -9633,7 +9636,7 @@
       </c>
       <c r="E24" s="88"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="93" t="s">
         <v>277</v>
       </c>
@@ -9648,7 +9651,7 @@
       </c>
       <c r="E25" s="88"/>
     </row>
-    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="94" t="s">
         <v>277</v>
       </c>
@@ -9663,7 +9666,7 @@
       </c>
       <c r="E26" s="79"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="93" t="s">
         <v>277</v>
       </c>
@@ -9678,7 +9681,7 @@
       </c>
       <c r="E27" s="88"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="93" t="s">
         <v>277</v>
       </c>
@@ -9693,7 +9696,7 @@
       </c>
       <c r="E28" s="88"/>
     </row>
-    <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="94" t="s">
         <v>277</v>
       </c>
@@ -9708,7 +9711,7 @@
       </c>
       <c r="E29" s="79"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="93" t="s">
         <v>277</v>
       </c>
@@ -9723,7 +9726,7 @@
       </c>
       <c r="E30" s="88"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="93" t="s">
         <v>277</v>
       </c>
@@ -9738,7 +9741,7 @@
       </c>
       <c r="E31" s="88"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="93" t="s">
         <v>277</v>
       </c>
@@ -9753,7 +9756,7 @@
       </c>
       <c r="E32" s="88"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="93" t="s">
         <v>277</v>
       </c>
@@ -9768,7 +9771,7 @@
       </c>
       <c r="E33" s="88"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="93" t="s">
         <v>277</v>
       </c>
@@ -9783,7 +9786,7 @@
       </c>
       <c r="E34" s="88"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="93" t="s">
         <v>277</v>
       </c>
@@ -9798,7 +9801,7 @@
       </c>
       <c r="E35" s="88"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="94" t="s">
         <v>277</v>
       </c>
@@ -9813,7 +9816,7 @@
       </c>
       <c r="E36" s="79"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="93" t="s">
         <v>277</v>
       </c>
@@ -9828,7 +9831,7 @@
       </c>
       <c r="E37" s="88"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="93" t="s">
         <v>277</v>
       </c>
@@ -9843,7 +9846,7 @@
       </c>
       <c r="E38" s="88"/>
     </row>
-    <row r="39" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="94" t="s">
         <v>277</v>
       </c>
@@ -9858,7 +9861,7 @@
       </c>
       <c r="E39" s="79"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="94" t="s">
         <v>277</v>
       </c>
@@ -9873,7 +9876,7 @@
       </c>
       <c r="E40" s="79"/>
     </row>
-    <row r="41" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="94" t="s">
         <v>277</v>
       </c>
@@ -9888,7 +9891,7 @@
       </c>
       <c r="E41" s="79"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="93" t="s">
         <v>277</v>
       </c>
@@ -9903,7 +9906,7 @@
       </c>
       <c r="E42" s="88"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="93" t="s">
         <v>277</v>
       </c>
@@ -9918,7 +9921,7 @@
       </c>
       <c r="E43" s="88"/>
     </row>
-    <row r="44" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="94" t="s">
         <v>277</v>
       </c>
@@ -9933,7 +9936,7 @@
       </c>
       <c r="E44" s="79"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="93" t="s">
         <v>277</v>
       </c>
@@ -9948,7 +9951,7 @@
       </c>
       <c r="E45" s="88"/>
     </row>
-    <row r="46" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="94" t="s">
         <v>277</v>
       </c>
@@ -9963,7 +9966,7 @@
       </c>
       <c r="E46" s="79"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="93" t="s">
         <v>277</v>
       </c>
@@ -9978,7 +9981,7 @@
       </c>
       <c r="E47" s="88"/>
     </row>
-    <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="94" t="s">
         <v>277</v>
       </c>
@@ -9993,7 +9996,7 @@
       </c>
       <c r="E48" s="79"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="93" t="s">
         <v>277</v>
       </c>
@@ -10008,7 +10011,7 @@
       </c>
       <c r="E49" s="88"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="93" t="s">
         <v>277</v>
       </c>
@@ -10023,7 +10026,7 @@
       </c>
       <c r="E50" s="88"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="93" t="s">
         <v>277</v>
       </c>
@@ -10038,7 +10041,7 @@
       </c>
       <c r="E51" s="88"/>
     </row>
-    <row r="52" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="94" t="s">
         <v>277</v>
       </c>
@@ -10053,7 +10056,7 @@
       </c>
       <c r="E52" s="79"/>
     </row>
-    <row r="53" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="95" t="s">
         <v>277</v>
       </c>
@@ -10076,9 +10079,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A229FC6-FA70-4A03-9310-422BE3A5FD27}">
   <dimension ref="A1:E42"/>
-  <sheetFormatPr defaultColWidth="37.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="37.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
@@ -10095,7 +10098,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="90" t="s">
         <v>277</v>
       </c>
@@ -10112,7 +10115,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="93" t="s">
         <v>277</v>
       </c>
@@ -10127,7 +10130,7 @@
       </c>
       <c r="E3" s="88"/>
     </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="93" t="s">
         <v>277</v>
       </c>
@@ -10142,7 +10145,7 @@
       </c>
       <c r="E4" s="88"/>
     </row>
-    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="93" t="s">
         <v>277</v>
       </c>
@@ -10157,7 +10160,7 @@
       </c>
       <c r="E5" s="88"/>
     </row>
-    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="93" t="s">
         <v>277</v>
       </c>
@@ -10172,7 +10175,7 @@
       </c>
       <c r="E6" s="88"/>
     </row>
-    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="93" t="s">
         <v>277</v>
       </c>
@@ -10187,7 +10190,7 @@
       </c>
       <c r="E7" s="88"/>
     </row>
-    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="93" t="s">
         <v>277</v>
       </c>
@@ -10202,7 +10205,7 @@
       </c>
       <c r="E8" s="88"/>
     </row>
-    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="93" t="s">
         <v>277</v>
       </c>
@@ -10217,7 +10220,7 @@
       </c>
       <c r="E9" s="88"/>
     </row>
-    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="93" t="s">
         <v>277</v>
       </c>
@@ -10232,7 +10235,7 @@
       </c>
       <c r="E10" s="88"/>
     </row>
-    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="94" t="s">
         <v>277</v>
       </c>
@@ -10247,7 +10250,7 @@
       </c>
       <c r="E11" s="79"/>
     </row>
-    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="94" t="s">
         <v>277</v>
       </c>
@@ -10262,7 +10265,7 @@
       </c>
       <c r="E12" s="79"/>
     </row>
-    <row r="13" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="97" t="s">
         <v>277</v>
       </c>
@@ -10279,7 +10282,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="93" t="s">
         <v>277</v>
       </c>
@@ -10294,7 +10297,7 @@
       </c>
       <c r="E14" s="88"/>
     </row>
-    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="93" t="s">
         <v>277</v>
       </c>
@@ -10309,7 +10312,7 @@
       </c>
       <c r="E15" s="88"/>
     </row>
-    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="93" t="s">
         <v>277</v>
       </c>
@@ -10324,7 +10327,7 @@
       </c>
       <c r="E16" s="88"/>
     </row>
-    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="93" t="s">
         <v>277</v>
       </c>
@@ -10339,7 +10342,7 @@
       </c>
       <c r="E17" s="88"/>
     </row>
-    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="93" t="s">
         <v>277</v>
       </c>
@@ -10354,7 +10357,7 @@
       </c>
       <c r="E18" s="88"/>
     </row>
-    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="93" t="s">
         <v>277</v>
       </c>
@@ -10369,7 +10372,7 @@
       </c>
       <c r="E19" s="88"/>
     </row>
-    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="93" t="s">
         <v>277</v>
       </c>
@@ -10384,7 +10387,7 @@
       </c>
       <c r="E20" s="88"/>
     </row>
-    <row r="21" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="94" t="s">
         <v>277</v>
       </c>
@@ -10399,7 +10402,7 @@
       </c>
       <c r="E21" s="79"/>
     </row>
-    <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="93" t="s">
         <v>277</v>
       </c>
@@ -10414,7 +10417,7 @@
       </c>
       <c r="E22" s="88"/>
     </row>
-    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="93" t="s">
         <v>277</v>
       </c>
@@ -10429,7 +10432,7 @@
       </c>
       <c r="E23" s="88"/>
     </row>
-    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="93" t="s">
         <v>277</v>
       </c>
@@ -10444,7 +10447,7 @@
       </c>
       <c r="E24" s="88"/>
     </row>
-    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="93" t="s">
         <v>277</v>
       </c>
@@ -10459,7 +10462,7 @@
       </c>
       <c r="E25" s="88"/>
     </row>
-    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="93" t="s">
         <v>277</v>
       </c>
@@ -10474,7 +10477,7 @@
       </c>
       <c r="E26" s="88"/>
     </row>
-    <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="93" t="s">
         <v>277</v>
       </c>
@@ -10489,7 +10492,7 @@
       </c>
       <c r="E27" s="88"/>
     </row>
-    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="94" t="s">
         <v>277</v>
       </c>
@@ -10504,7 +10507,7 @@
       </c>
       <c r="E28" s="79"/>
     </row>
-    <row r="29" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="94" t="s">
         <v>277</v>
       </c>
@@ -10519,7 +10522,7 @@
       </c>
       <c r="E29" s="79"/>
     </row>
-    <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="94" t="s">
         <v>277</v>
       </c>
@@ -10534,7 +10537,7 @@
       </c>
       <c r="E30" s="79"/>
     </row>
-    <row r="31" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="94" t="s">
         <v>277</v>
       </c>
@@ -10549,7 +10552,7 @@
       </c>
       <c r="E31" s="79"/>
     </row>
-    <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="93" t="s">
         <v>277</v>
       </c>
@@ -10564,7 +10567,7 @@
       </c>
       <c r="E32" s="88"/>
     </row>
-    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="94" t="s">
         <v>277</v>
       </c>
@@ -10579,7 +10582,7 @@
       </c>
       <c r="E33" s="79"/>
     </row>
-    <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="93" t="s">
         <v>277</v>
       </c>
@@ -10594,7 +10597,7 @@
       </c>
       <c r="E34" s="88"/>
     </row>
-    <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="93" t="s">
         <v>277</v>
       </c>
@@ -10609,7 +10612,7 @@
       </c>
       <c r="E35" s="88"/>
     </row>
-    <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="93" t="s">
         <v>277</v>
       </c>
@@ -10624,7 +10627,7 @@
       </c>
       <c r="E36" s="88"/>
     </row>
-    <row r="37" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="94" t="s">
         <v>277</v>
       </c>
@@ -10639,7 +10642,7 @@
       </c>
       <c r="E37" s="79"/>
     </row>
-    <row r="38" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="93" t="s">
         <v>277</v>
       </c>
@@ -10654,7 +10657,7 @@
       </c>
       <c r="E38" s="88"/>
     </row>
-    <row r="39" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="93" t="s">
         <v>277</v>
       </c>
@@ -10669,7 +10672,7 @@
       </c>
       <c r="E39" s="88"/>
     </row>
-    <row r="40" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="93" t="s">
         <v>277</v>
       </c>
@@ -10684,7 +10687,7 @@
       </c>
       <c r="E40" s="88"/>
     </row>
-    <row r="41" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="93" t="s">
         <v>277</v>
       </c>
@@ -10699,7 +10702,7 @@
       </c>
       <c r="E41" s="88"/>
     </row>
-    <row r="42" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="101" t="s">
         <v>277</v>
       </c>
